--- a/Sales_Fr_data/Sales_data.xlsx
+++ b/Sales_Fr_data/Sales_data.xlsx
@@ -238,6 +238,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -717,7 +720,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1041,9 +1044,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C1197"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -14211,5 +14217,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>